--- a/network_data.xlsx
+++ b/network_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\223106456\Desktop\PyPSA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36472701-7BB8-404F-B343-3CBDB5B1EA7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E423A08-9646-49D8-A899-5CB7D66CE9D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="44">
   <si>
     <t>Bus Name</t>
   </si>
@@ -170,6 +170,9 @@
   </si>
   <si>
     <t>Impedance (x)</t>
+  </si>
+  <si>
+    <t>Resistance ®</t>
   </si>
 </sst>
 </file>
@@ -678,17 +681,18 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB5A70A1-4A88-4DB1-8204-88DDA72E8E47}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.1796875" customWidth="1"/>
     <col min="2" max="2" width="10.1796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.81640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19.08984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.08984375" customWidth="1"/>
+    <col min="6" max="6" width="13.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -702,10 +706,13 @@
         <v>4</v>
       </c>
       <c r="E1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>37</v>
       </c>
@@ -719,10 +726,13 @@
         <v>100</v>
       </c>
       <c r="E2">
+        <v>0.01</v>
+      </c>
+      <c r="F2">
         <v>0.02</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>38</v>
       </c>
@@ -736,10 +746,13 @@
         <v>100</v>
       </c>
       <c r="E3">
+        <v>0.01</v>
+      </c>
+      <c r="F3">
         <v>0.05</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>39</v>
       </c>
@@ -753,10 +766,13 @@
         <v>100</v>
       </c>
       <c r="E4">
+        <v>0.01</v>
+      </c>
+      <c r="F4">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>40</v>
       </c>
@@ -770,10 +786,13 @@
         <v>100</v>
       </c>
       <c r="E5">
+        <v>0.01</v>
+      </c>
+      <c r="F5">
         <v>0.1</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>41</v>
       </c>
@@ -787,6 +806,9 @@
         <v>100</v>
       </c>
       <c r="E6">
+        <v>0.01</v>
+      </c>
+      <c r="F6">
         <v>0.01</v>
       </c>
     </row>

--- a/network_data.xlsx
+++ b/network_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\223106456\Desktop\PyPSA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E423A08-9646-49D8-A899-5CB7D66CE9D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C08C2410-2C52-4F30-8CE0-68EB0B302A1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -169,10 +169,10 @@
     <t>Line_3_4</t>
   </si>
   <si>
-    <t>Impedance (x)</t>
-  </si>
-  <si>
-    <t>Resistance ®</t>
+    <t>Resistance (r)</t>
+  </si>
+  <si>
+    <t>Reactance (x)</t>
   </si>
 </sst>
 </file>
@@ -706,10 +706,10 @@
         <v>4</v>
       </c>
       <c r="E1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F1" t="s">
         <v>43</v>
-      </c>
-      <c r="F1" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
